--- a/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ENGINEERING PROJECT/Setting Project environment/data_engineering_environment_setup.xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA ENGINEERING PROJECT/Setting Project environment/data_engineering_environment_setup.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Engineering Env Setup" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -434,12 +434,12 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Correct Answer</t>
+          <t>Explanation</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Explanation</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -454,15 +454,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Version control</t>
+          <t>Initialize git repository for version control.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Initialize git repository for version control.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -477,15 +476,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>venv</t>
+          <t>Python venv creates isolated environments for dependencies.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Python venv creates isolated environments for dependencies.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -500,15 +498,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>requirements.txt</t>
+          <t>requirements.txt lists all Python packages needed.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>requirements.txt lists all Python packages needed.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -523,15 +520,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Exclude files</t>
+          <t>It prevents committing sensitive or unnecessary files.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>It prevents committing sensitive or unnecessary files.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -546,15 +542,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>python -m venv data_env</t>
+          <t>This creates an isolated Python environment.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>This creates an isolated Python environment.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -576,12 +571,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>Environment inconsistencies cause these issues.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Environment inconsistencies cause these issues.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -596,15 +591,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Containerization</t>
+          <t>Docker creates consistent environments across machines.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker creates consistent environments across machines.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -619,15 +613,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Build image</t>
+          <t>It defines how to build a Docker container image.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>It defines how to build a Docker container image.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -642,15 +635,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>docker build</t>
+          <t>This creates a container image.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>This creates a container image.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -665,15 +657,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>.env file</t>
+          <t>.env files store environment variables locally.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>.env files store environment variables locally.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -688,15 +679,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>python-dotenv</t>
+          <t>The python-dotenv package loads .env files.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The python-dotenv package loads .env files.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -711,15 +701,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Automation</t>
+          <t>Makefiles automate common commands and workflows.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Makefiles automate common commands and workflows.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -741,12 +730,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Docker Compose orchestrates multiple services.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Docker Compose orchestrates multiple services.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -761,15 +750,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>It defines all services, networks, and volumes.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>It defines all services, networks, and volumes.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -784,15 +772,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>docker-compose up</t>
+          <t>This starts all defined services.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>This starts all defined services.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -807,15 +794,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Code quality</t>
+          <t>They run checks before code commits.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>They run checks before code commits.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -830,15 +816,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Black</t>
+          <t>Black automatically formats Python code.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Black automatically formats Python code.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -853,15 +838,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Export dependencies</t>
+          <t>It saves all installed packages to requirements.txt.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>It saves all installed packages to requirements.txt.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -876,15 +860,14 @@
           <t>One-word</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>pip install -r requirements.txt</t>
+          <t>This installs all listed packages.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>This installs all listed packages.</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -906,12 +889,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>Use environment-specific configuration files.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Use environment-specific configuration files.</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
